--- a/artfynd/A 22836-2021 artfynd.xlsx
+++ b/artfynd/A 22836-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22836-2021 artfynd.xlsx
+++ b/artfynd/A 22836-2021 artfynd.xlsx
@@ -12521,10 +12521,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119815639</v>
+        <v>119815612</v>
       </c>
       <c r="B115" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12537,21 +12537,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12561,10 +12561,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457788</v>
+        <v>457803</v>
       </c>
       <c r="R115" t="n">
-        <v>7073705</v>
+        <v>7073660</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12627,10 +12627,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119815612</v>
+        <v>119815639</v>
       </c>
       <c r="B116" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12643,21 +12643,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457803</v>
+        <v>457788</v>
       </c>
       <c r="R116" t="n">
-        <v>7073660</v>
+        <v>7073705</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 22836-2021 artfynd.xlsx
+++ b/artfynd/A 22836-2021 artfynd.xlsx
@@ -12521,10 +12521,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119815612</v>
+        <v>119815632</v>
       </c>
       <c r="B115" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12537,21 +12537,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12561,10 +12561,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457803</v>
+        <v>457764</v>
       </c>
       <c r="R115" t="n">
-        <v>7073660</v>
+        <v>7073676</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12627,10 +12627,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119815639</v>
+        <v>119815612</v>
       </c>
       <c r="B116" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12643,21 +12643,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457788</v>
+        <v>457803</v>
       </c>
       <c r="R116" t="n">
-        <v>7073705</v>
+        <v>7073660</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12733,7 +12733,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119815632</v>
+        <v>119815639</v>
       </c>
       <c r="B117" t="n">
         <v>78526</v>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457764</v>
+        <v>457788</v>
       </c>
       <c r="R117" t="n">
-        <v>7073676</v>
+        <v>7073705</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 22836-2021 artfynd.xlsx
+++ b/artfynd/A 22836-2021 artfynd.xlsx
@@ -12627,10 +12627,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119815612</v>
+        <v>119815639</v>
       </c>
       <c r="B116" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12643,21 +12643,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457803</v>
+        <v>457788</v>
       </c>
       <c r="R116" t="n">
-        <v>7073660</v>
+        <v>7073705</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12733,10 +12733,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119815639</v>
+        <v>119815612</v>
       </c>
       <c r="B117" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12749,21 +12749,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457788</v>
+        <v>457803</v>
       </c>
       <c r="R117" t="n">
-        <v>7073705</v>
+        <v>7073660</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 22836-2021 artfynd.xlsx
+++ b/artfynd/A 22836-2021 artfynd.xlsx
@@ -12521,10 +12521,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119815632</v>
+        <v>119815639</v>
       </c>
       <c r="B115" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12561,10 +12561,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457764</v>
+        <v>457788</v>
       </c>
       <c r="R115" t="n">
-        <v>7073676</v>
+        <v>7073705</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12627,10 +12627,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119815639</v>
+        <v>119815612</v>
       </c>
       <c r="B116" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12643,21 +12643,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457788</v>
+        <v>457803</v>
       </c>
       <c r="R116" t="n">
-        <v>7073705</v>
+        <v>7073660</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12733,10 +12733,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119815612</v>
+        <v>119815632</v>
       </c>
       <c r="B117" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12749,21 +12749,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457803</v>
+        <v>457764</v>
       </c>
       <c r="R117" t="n">
-        <v>7073660</v>
+        <v>7073676</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 22836-2021 artfynd.xlsx
+++ b/artfynd/A 22836-2021 artfynd.xlsx
@@ -12521,7 +12521,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119815639</v>
+        <v>119815632</v>
       </c>
       <c r="B115" t="n">
         <v>78542</v>
@@ -12561,10 +12561,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457788</v>
+        <v>457764</v>
       </c>
       <c r="R115" t="n">
-        <v>7073705</v>
+        <v>7073676</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12733,7 +12733,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119815632</v>
+        <v>119815639</v>
       </c>
       <c r="B117" t="n">
         <v>78542</v>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457764</v>
+        <v>457788</v>
       </c>
       <c r="R117" t="n">
-        <v>7073676</v>
+        <v>7073705</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 22836-2021 artfynd.xlsx
+++ b/artfynd/A 22836-2021 artfynd.xlsx
@@ -12521,10 +12521,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119815632</v>
+        <v>119815612</v>
       </c>
       <c r="B115" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12537,21 +12537,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12561,10 +12561,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>457764</v>
+        <v>457803</v>
       </c>
       <c r="R115" t="n">
-        <v>7073676</v>
+        <v>7073660</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12627,10 +12627,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119815612</v>
+        <v>119815639</v>
       </c>
       <c r="B116" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12643,21 +12643,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>457803</v>
+        <v>457788</v>
       </c>
       <c r="R116" t="n">
-        <v>7073660</v>
+        <v>7073705</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12733,7 +12733,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119815639</v>
+        <v>119815632</v>
       </c>
       <c r="B117" t="n">
         <v>78542</v>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>457788</v>
+        <v>457764</v>
       </c>
       <c r="R117" t="n">
-        <v>7073705</v>
+        <v>7073676</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
